--- a/tabtools/qa/output/regtab_ext_test13.xlsx
+++ b/tabtools/qa/output/regtab_ext_test13.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="896" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1008" uniqueCount="47">
   <si>
     <t>Test 13: Two Mixed Models</t>
   </si>
@@ -160,10 +160,2076 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="3913">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="4402">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -16702,7 +18768,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2913">
+  <borders count="3277">
     <border>
       <left/>
       <right/>
@@ -36710,11 +38776,2511 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2913">
+  <cellXfs count="3277">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -48169,6 +52735,1438 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="3912" fillId="0" borderId="2912" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2913" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2914" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2915" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2916" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2917" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2918" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2919" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2920" xfId="0"/>
+    <xf numFmtId="0" fontId="3913" fillId="0" borderId="2921" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3914" fillId="0" borderId="2922" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3915" fillId="0" borderId="2923" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3916" fillId="0" borderId="2924" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3917" fillId="0" borderId="2925" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3918" fillId="0" borderId="2926" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3920" fillId="0" borderId="2927" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3922" fillId="0" borderId="2928" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3924" fillId="0" borderId="2929" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3925" fillId="0" borderId="2930" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3926" fillId="0" borderId="2931" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3927" fillId="0" borderId="2932" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3928" fillId="0" borderId="2933" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3929" fillId="0" borderId="2934" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3930" fillId="0" borderId="2935" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3931" fillId="0" borderId="2936" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3932" fillId="0" borderId="2937" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3933" fillId="0" borderId="2938" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3934" fillId="0" borderId="2939" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3935" fillId="0" borderId="2940" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3936" fillId="0" borderId="2941" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3937" fillId="0" borderId="2942" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3938" fillId="0" borderId="2943" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3939" fillId="0" borderId="2944" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3940" fillId="0" borderId="2945" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3941" fillId="0" borderId="2946" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3942" fillId="0" borderId="2947" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3943" fillId="0" borderId="2948" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3944" fillId="0" borderId="2949" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3945" fillId="0" borderId="2950" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3946" fillId="0" borderId="2951" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3948" fillId="0" borderId="2952" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3950" fillId="0" borderId="2953" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3952" fillId="0" borderId="2954" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3953" fillId="0" borderId="2955" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3954" fillId="0" borderId="2956" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3955" fillId="0" borderId="2957" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3956" fillId="0" borderId="2958" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3957" fillId="0" borderId="2959" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3958" fillId="0" borderId="2960" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3959" fillId="0" borderId="2961" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3960" fillId="0" borderId="2962" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3961" fillId="0" borderId="2963" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3962" fillId="0" borderId="2964" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3963" fillId="0" borderId="2965" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3964" fillId="0" borderId="2966" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3965" fillId="0" borderId="2967" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3966" fillId="0" borderId="2968" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3967" fillId="0" borderId="2969" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3968" fillId="0" borderId="2970" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3969" fillId="0" borderId="2971" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3970" fillId="0" borderId="2972" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3971" fillId="0" borderId="2973" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3972" fillId="0" borderId="2974" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3973" fillId="0" borderId="2975" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3974" fillId="0" borderId="2976" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3975" fillId="0" borderId="2977" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3976" fillId="0" borderId="2978" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3977" fillId="0" borderId="2979" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3978" fillId="0" borderId="2980" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3979" fillId="0" borderId="2981" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3980" fillId="0" borderId="2982" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3981" fillId="0" borderId="2983" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3982" fillId="0" borderId="2984" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3983" fillId="0" borderId="2985" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3984" fillId="0" borderId="2986" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3986" fillId="0" borderId="2987" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3988" fillId="0" borderId="2988" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3990" fillId="0" borderId="2989" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3992" fillId="0" borderId="2990" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3994" fillId="0" borderId="2991" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3996" fillId="0" borderId="2992" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3998" fillId="0" borderId="2993" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4000" fillId="0" borderId="2994" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4001" fillId="0" borderId="2995" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4002" fillId="0" borderId="2996" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4003" fillId="0" borderId="2997" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4004" fillId="0" borderId="2998" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4005" fillId="0" borderId="2999" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4006" fillId="0" borderId="3000" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4007" fillId="0" borderId="3001" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4008" fillId="0" borderId="3002" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4009" fillId="0" borderId="3003" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4010" fillId="0" borderId="3004" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4011" fillId="0" borderId="3005" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4012" fillId="0" borderId="3006" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4013" fillId="0" borderId="3007" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4014" fillId="0" borderId="3008" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4015" fillId="0" borderId="3009" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4016" fillId="0" borderId="3010" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4017" fillId="0" borderId="3011" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4018" fillId="0" borderId="3012" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4019" fillId="0" borderId="3013" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4020" fillId="0" borderId="3014" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4021" fillId="0" borderId="3015" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4022" fillId="0" borderId="3016" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4024" fillId="0" borderId="3017" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4026" fillId="0" borderId="3018" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4028" fillId="0" borderId="3019" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4030" fillId="0" borderId="3020" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4032" fillId="0" borderId="3021" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4034" fillId="0" borderId="3022" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4036" fillId="0" borderId="3023" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4037" fillId="0" borderId="3024" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4038" fillId="0" borderId="3025" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4039" fillId="0" borderId="3026" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4040" fillId="0" borderId="3027" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4041" fillId="0" borderId="3028" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4042" fillId="0" borderId="3029" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4043" fillId="0" borderId="3030" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4044" fillId="0" borderId="3031" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4045" fillId="0" borderId="3032" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4046" fillId="0" borderId="3033" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4047" fillId="0" borderId="3034" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4048" fillId="0" borderId="3035" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4049" fillId="0" borderId="3036" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4050" fillId="0" borderId="3037" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4051" fillId="0" borderId="3038" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4052" fillId="0" borderId="3039" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4053" fillId="0" borderId="3040" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4054" fillId="0" borderId="3041" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4055" fillId="0" borderId="3042" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4056" fillId="0" borderId="3043" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4057" fillId="0" borderId="3044" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4058" fillId="0" borderId="3045" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4059" fillId="0" borderId="3046" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4060" fillId="0" borderId="3047" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4061" fillId="0" borderId="3048" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4062" fillId="0" borderId="3049" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4063" fillId="0" borderId="3050" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4064" fillId="0" borderId="3051" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4065" fillId="0" borderId="3052" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4066" fillId="0" borderId="3053" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4067" fillId="0" borderId="3054" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4068" fillId="0" borderId="3055" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4069" fillId="0" borderId="3056" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4070" fillId="0" borderId="3057" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4071" fillId="0" borderId="3058" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4072" fillId="0" borderId="3059" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4073" fillId="0" borderId="3060" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4074" fillId="0" borderId="3061" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4075" fillId="0" borderId="3062" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4076" fillId="0" borderId="3063" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4077" fillId="0" borderId="3064" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4078" fillId="0" borderId="3065" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4079" fillId="0" borderId="3066" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4080" fillId="0" borderId="3067" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4081" fillId="0" borderId="3068" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4082" fillId="0" borderId="3069" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4083" fillId="0" borderId="3070" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4084" fillId="0" borderId="3071" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4085" fillId="0" borderId="3072" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4086" fillId="0" borderId="3073" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4087" fillId="0" borderId="3074" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4088" fillId="0" borderId="3075" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4089" fillId="0" borderId="3076" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4090" fillId="0" borderId="3077" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4091" fillId="0" borderId="3078" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4092" fillId="0" borderId="3079" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4093" fillId="0" borderId="3080" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4094" fillId="0" borderId="3081" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4095" fillId="0" borderId="3082" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4096" fillId="0" borderId="3083" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4097" fillId="0" borderId="3084" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4098" fillId="0" borderId="3085" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4099" fillId="0" borderId="3086" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4100" fillId="0" borderId="3087" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4101" fillId="0" borderId="3088" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4102" fillId="0" borderId="3089" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4103" fillId="0" borderId="3090" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4104" fillId="0" borderId="3091" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4105" fillId="0" borderId="3092" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4106" fillId="0" borderId="3093" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4107" fillId="0" borderId="3094" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4108" fillId="0" borderId="3095" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4109" fillId="0" borderId="3096" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4110" fillId="0" borderId="3097" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4111" fillId="0" borderId="3098" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4112" fillId="0" borderId="3099" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4113" fillId="0" borderId="3100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4114" fillId="0" borderId="3101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4115" fillId="0" borderId="3102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4116" fillId="0" borderId="3103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4117" fillId="0" borderId="3104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4118" fillId="0" borderId="3105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4119" fillId="0" borderId="3106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4120" fillId="0" borderId="3107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4121" fillId="0" borderId="3108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4122" fillId="0" borderId="3109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4123" fillId="0" borderId="3110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4124" fillId="0" borderId="3111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4125" fillId="0" borderId="3112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4126" fillId="0" borderId="3113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4127" fillId="0" borderId="3114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4128" fillId="0" borderId="3115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4129" fillId="0" borderId="3116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4130" fillId="0" borderId="3117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4131" fillId="0" borderId="3118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4132" fillId="0" borderId="3119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4133" fillId="0" borderId="3120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4134" fillId="0" borderId="3121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4135" fillId="0" borderId="3122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4136" fillId="0" borderId="3123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4137" fillId="0" borderId="3124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4138" fillId="0" borderId="3125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4139" fillId="0" borderId="3126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4140" fillId="0" borderId="3127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4141" fillId="0" borderId="3128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4142" fillId="0" borderId="3129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4143" fillId="0" borderId="3130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4144" fillId="0" borderId="3131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4145" fillId="0" borderId="3132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4146" fillId="0" borderId="3133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4147" fillId="0" borderId="3134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4148" fillId="0" borderId="3135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4149" fillId="0" borderId="3136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4150" fillId="0" borderId="3137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4151" fillId="0" borderId="3138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4152" fillId="0" borderId="3139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4153" fillId="0" borderId="3140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4154" fillId="0" borderId="3141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4155" fillId="0" borderId="3142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4156" fillId="0" borderId="3143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4157" fillId="0" borderId="3144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4158" fillId="0" borderId="3145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4159" fillId="0" borderId="3146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4160" fillId="0" borderId="3147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4161" fillId="0" borderId="3148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4162" fillId="0" borderId="3149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4163" fillId="0" borderId="3150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4164" fillId="0" borderId="3151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4165" fillId="0" borderId="3152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4166" fillId="0" borderId="3153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4167" fillId="0" borderId="3154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4168" fillId="0" borderId="3155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4169" fillId="0" borderId="3156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4170" fillId="0" borderId="3157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4171" fillId="0" borderId="3158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4172" fillId="0" borderId="3159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4173" fillId="0" borderId="3160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4174" fillId="0" borderId="3161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4175" fillId="0" borderId="3162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4176" fillId="0" borderId="3163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4177" fillId="0" borderId="3164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4179" fillId="0" borderId="3165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4181" fillId="0" borderId="3166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4183" fillId="0" borderId="3167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4185" fillId="0" borderId="3168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4187" fillId="0" borderId="3169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4189" fillId="0" borderId="3170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4191" fillId="0" borderId="3171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4193" fillId="0" borderId="3172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4195" fillId="0" borderId="3173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4197" fillId="0" borderId="3174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4199" fillId="0" borderId="3175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4201" fillId="0" borderId="3176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4203" fillId="0" borderId="3177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4205" fillId="0" borderId="3178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4207" fillId="0" borderId="3179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4209" fillId="0" borderId="3180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4211" fillId="0" borderId="3181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4213" fillId="0" borderId="3182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4215" fillId="0" borderId="3183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4217" fillId="0" borderId="3184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4219" fillId="0" borderId="3185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4221" fillId="0" borderId="3186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4223" fillId="0" borderId="3187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4225" fillId="0" borderId="3188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4227" fillId="0" borderId="3189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4229" fillId="0" borderId="3190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4231" fillId="0" borderId="3191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4233" fillId="0" borderId="3192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4235" fillId="0" borderId="3193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4237" fillId="0" borderId="3194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4239" fillId="0" borderId="3195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4241" fillId="0" borderId="3196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4243" fillId="0" borderId="3197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4245" fillId="0" borderId="3198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4247" fillId="0" borderId="3199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4249" fillId="0" borderId="3200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4251" fillId="0" borderId="3201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4253" fillId="0" borderId="3202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4255" fillId="0" borderId="3203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4257" fillId="0" borderId="3204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4259" fillId="0" borderId="3205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4261" fillId="0" borderId="3206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4263" fillId="0" borderId="3207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4265" fillId="0" borderId="3208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4267" fillId="0" borderId="3209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4269" fillId="0" borderId="3210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4271" fillId="0" borderId="3211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4273" fillId="0" borderId="3212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4275" fillId="0" borderId="3213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4277" fillId="0" borderId="3214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4279" fillId="0" borderId="3215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4281" fillId="0" borderId="3216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4283" fillId="0" borderId="3217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4285" fillId="0" borderId="3218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4287" fillId="0" borderId="3219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4289" fillId="0" borderId="3220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4291" fillId="0" borderId="3221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4293" fillId="0" borderId="3222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4295" fillId="0" borderId="3223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4297" fillId="0" borderId="3224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4299" fillId="0" borderId="3225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4301" fillId="0" borderId="3226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4303" fillId="0" borderId="3227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4305" fillId="0" borderId="3228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4307" fillId="0" borderId="3229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4309" fillId="0" borderId="3230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4311" fillId="0" borderId="3231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4313" fillId="0" borderId="3232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4315" fillId="0" borderId="3233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4317" fillId="0" borderId="3234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4319" fillId="0" borderId="3235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4321" fillId="0" borderId="3236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4323" fillId="0" borderId="3237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4325" fillId="0" borderId="3238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4327" fillId="0" borderId="3239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4329" fillId="0" borderId="3240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4331" fillId="0" borderId="3241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4333" fillId="0" borderId="3242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4335" fillId="0" borderId="3243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4337" fillId="0" borderId="3244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4339" fillId="0" borderId="3245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4341" fillId="0" borderId="3246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4343" fillId="0" borderId="3247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4345" fillId="0" borderId="3248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4347" fillId="0" borderId="3249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4349" fillId="0" borderId="3250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4351" fillId="0" borderId="3251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4353" fillId="0" borderId="3252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4355" fillId="0" borderId="3253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4357" fillId="0" borderId="3254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4359" fillId="0" borderId="3255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4361" fillId="0" borderId="3256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4363" fillId="0" borderId="3257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4365" fillId="0" borderId="3258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4367" fillId="0" borderId="3259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4369" fillId="0" borderId="3260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4371" fillId="0" borderId="3261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4373" fillId="0" borderId="3262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4375" fillId="0" borderId="3263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4377" fillId="0" borderId="3264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4379" fillId="0" borderId="3265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4381" fillId="0" borderId="3266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4383" fillId="0" borderId="3267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4385" fillId="0" borderId="3268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4387" fillId="0" borderId="3269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4389" fillId="0" borderId="3270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4391" fillId="0" borderId="3271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4393" fillId="0" borderId="3272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4395" fillId="0" borderId="3273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4397" fillId="0" borderId="3274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4399" fillId="0" borderId="3275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4401" fillId="0" borderId="3276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -48184,376 +54182,376 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19.7109375" style="2550" customWidth="true"/>
-    <col min="3" max="3" width="5.11328125" style="2551" customWidth="true"/>
-    <col min="6" max="6" width="5.11328125" style="2552" customWidth="true"/>
-    <col min="4" max="4" width="11.11328125" style="2553" customWidth="true"/>
-    <col min="7" max="7" width="11.11328125" style="2554" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="2555" customWidth="true"/>
-    <col min="8" max="8" width="7.7109375" style="2556" customWidth="true"/>
+    <col min="2" max="2" width="19.7109375" style="2914" customWidth="true"/>
+    <col min="3" max="3" width="5.11328125" style="2915" customWidth="true"/>
+    <col min="6" max="6" width="5.11328125" style="2916" customWidth="true"/>
+    <col min="4" max="4" width="11.11328125" style="2917" customWidth="true"/>
+    <col min="7" max="7" width="11.11328125" style="2918" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="2919" customWidth="true"/>
+    <col min="8" max="8" width="7.7109375" style="2920" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="2549" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="2801" t="s">
+    <row r="1" s="2913" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="3165" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2802" t="s">
+      <c r="B1" s="3166" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2803" t="s">
+      <c r="C1" s="3167" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2804" t="s">
+      <c r="D1" s="3168" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2805" t="s">
+      <c r="E1" s="3169" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2806" t="s">
+      <c r="F1" s="3170" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="2807" t="s">
+      <c r="G1" s="3171" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="2808" t="s">
+      <c r="H1" s="3172" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2809" t="s">
+      <c r="A2" s="3173" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2810" t="s">
+      <c r="B2" s="3174" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2811" t="s">
+      <c r="C2" s="3175" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2812" t="s">
+      <c r="D2" s="3176" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2813" t="s">
+      <c r="E2" s="3177" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="2814" t="s">
+      <c r="F2" s="3178" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="2815" t="s">
+      <c r="G2" s="3179" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="2816" t="s">
+      <c r="H2" s="3180" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2817" t="s">
+      <c r="A3" s="3181" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2818" t="s">
+      <c r="B3" s="3182" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2819" t="s">
+      <c r="C3" s="3183" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2820" t="s">
+      <c r="D3" s="3184" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="2821" t="s">
+      <c r="E3" s="3185" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="2822" t="s">
+      <c r="F3" s="3186" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2823" t="s">
+      <c r="G3" s="3187" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="2824" t="s">
+      <c r="H3" s="3188" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2825" t="s">
+      <c r="A4" s="3189" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2826" t="s">
+      <c r="B4" s="3190" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="2827" t="s">
+      <c r="C4" s="3191" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2828" t="s">
+      <c r="D4" s="3192" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="2829" t="s">
+      <c r="E4" s="3193" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="2830" t="s">
+      <c r="F4" s="3194" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="2831" t="s">
+      <c r="G4" s="3195" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="2832" t="s">
+      <c r="H4" s="3196" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2833" t="s">
+      <c r="A5" s="3197" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="2834" t="s">
+      <c r="B5" s="3198" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2835" t="s">
+      <c r="C5" s="3199" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="2836" t="s">
+      <c r="D5" s="3200" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="2837" t="s">
+      <c r="E5" s="3201" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="2838" t="s">
+      <c r="F5" s="3202" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="2839" t="s">
+      <c r="G5" s="3203" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="2840" t="s">
+      <c r="H5" s="3204" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2841" t="s">
+      <c r="A6" s="3205" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="2842" t="s">
+      <c r="B6" s="3206" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2843" t="s">
+      <c r="C6" s="3207" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="2844" t="s">
+      <c r="D6" s="3208" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="2845" t="s">
+      <c r="E6" s="3209" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="2846" t="s">
+      <c r="F6" s="3210" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="2847" t="s">
+      <c r="G6" s="3211" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="2848" t="s">
+      <c r="H6" s="3212" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2849" t="s">
+      <c r="A7" s="3213" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="2850" t="s">
+      <c r="B7" s="3214" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="2851" t="s">
+      <c r="C7" s="3215" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="2852" t="s">
+      <c r="D7" s="3216" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="2853" t="s">
+      <c r="E7" s="3217" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="2854" t="s">
+      <c r="F7" s="3218" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="2855" t="s">
+      <c r="G7" s="3219" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="2856" t="s">
+      <c r="H7" s="3220" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2857" t="s">
+      <c r="A8" s="3221" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="2858" t="s">
+      <c r="B8" s="3222" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="2859" t="s">
+      <c r="C8" s="3223" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="2860" t="s">
+      <c r="D8" s="3224" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="2861" t="s">
+      <c r="E8" s="3225" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="2862" t="s">
+      <c r="F8" s="3226" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="2863" t="s">
+      <c r="G8" s="3227" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="2864" t="s">
+      <c r="H8" s="3228" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2865" t="s">
+      <c r="A9" s="3229" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="2866" t="s">
+      <c r="B9" s="3230" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="2867" t="s">
+      <c r="C9" s="3231" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="2868" t="s">
+      <c r="D9" s="3232" t="s">
         <v>1</v>
       </c>
-      <c r="E9" s="2869" t="s">
+      <c r="E9" s="3233" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="2870" t="s">
+      <c r="F9" s="3234" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="2871" t="s">
+      <c r="G9" s="3235" t="s">
         <v>1</v>
       </c>
-      <c r="H9" s="2872" t="s">
+      <c r="H9" s="3236" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2873" t="s">
+      <c r="A10" s="3237" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="2874" t="s">
+      <c r="B10" s="3238" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2875" t="s">
+      <c r="C10" s="3239" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="2876" t="s">
+      <c r="D10" s="3240" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="2877" t="s">
+      <c r="E10" s="3241" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="2878" t="s">
+      <c r="F10" s="3242" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="2879" t="s">
+      <c r="G10" s="3243" t="s">
         <v>1</v>
       </c>
-      <c r="H10" s="2880" t="s">
+      <c r="H10" s="3244" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2881" t="s">
+      <c r="A11" s="3245" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="2882" t="s">
+      <c r="B11" s="3246" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="2883" t="s">
+      <c r="C11" s="3247" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="2884" t="s">
+      <c r="D11" s="3248" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="2885" t="s">
+      <c r="E11" s="3249" t="s">
         <v>1</v>
       </c>
-      <c r="F11" s="2886" t="s">
+      <c r="F11" s="3250" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="2887" t="s">
+      <c r="G11" s="3251" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="2888" t="s">
+      <c r="H11" s="3252" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2889" t="s">
+      <c r="A12" s="3253" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="2890" t="s">
+      <c r="B12" s="3254" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="2891" t="s">
+      <c r="C12" s="3255" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="2892" t="s">
+      <c r="D12" s="3256" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="2893" t="s">
+      <c r="E12" s="3257" t="s">
         <v>1</v>
       </c>
-      <c r="F12" s="2894" t="s">
+      <c r="F12" s="3258" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="2895" t="s">
+      <c r="G12" s="3259" t="s">
         <v>1</v>
       </c>
-      <c r="H12" s="2896" t="s">
+      <c r="H12" s="3260" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2897" t="s">
+      <c r="A13" s="3261" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="2898" t="s">
+      <c r="B13" s="3262" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="2899" t="s">
+      <c r="C13" s="3263" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="2900" t="s">
+      <c r="D13" s="3264" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="2901" t="s">
+      <c r="E13" s="3265" t="s">
         <v>1</v>
       </c>
-      <c r="F13" s="2902" t="s">
+      <c r="F13" s="3266" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="2903" t="s">
+      <c r="G13" s="3267" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="2904" t="s">
+      <c r="H13" s="3268" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2905" t="s">
+      <c r="A14" s="3269" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="2906" t="s">
+      <c r="B14" s="3270" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="2907" t="s">
+      <c r="C14" s="3271" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="2908" t="s">
+      <c r="D14" s="3272" t="s">
         <v>1</v>
       </c>
-      <c r="E14" s="2909" t="s">
+      <c r="E14" s="3273" t="s">
         <v>1</v>
       </c>
-      <c r="F14" s="2910" t="s">
+      <c r="F14" s="3274" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="2911" t="s">
+      <c r="G14" s="3275" t="s">
         <v>1</v>
       </c>
-      <c r="H14" s="2912" t="s">
+      <c r="H14" s="3276" t="s">
         <v>1</v>
       </c>
     </row>
